--- a/saida/isaias_taxa_servico_2026-10-01_a_20.xlsx
+++ b/saida/isaias_taxa_servico_2026-10-01_a_20.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W97"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>PDV 01 em 43 de 68 casamentos exatos</t>
+          <t>PDV 01 em 47 de 72 casamentos exatos</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4207,27 +4207,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>43223</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4242,45 +4242,48 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AUGUSTO DE OLIVEIRA GOMES</t>
-        </is>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>6</v>
       </c>
       <c r="K36" t="n">
-        <v>51</v>
+        <v>143.5</v>
       </c>
       <c r="L36" t="n">
-        <v>56.1</v>
+        <v>157.85</v>
       </c>
       <c r="M36" t="n">
-        <v>5.1</v>
+        <v>14.35</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>TFI5EE8C</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>433456</t>
+          <t>SE001000000000LTU73FWKBD10OF3L03V8</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PDV 02 em 985 de 1160 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="S36" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4294,7 +4297,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>ver observação</t>
+          <t>fechada</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4326,12 +4329,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>43316</t>
+          <t>43322</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4346,24 +4349,24 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K37" t="n">
-        <v>143.5</v>
+        <v>93</v>
       </c>
       <c r="L37" t="n">
-        <v>157.85</v>
+        <v>102.3</v>
       </c>
       <c r="M37" t="n">
-        <v>14.35</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4373,12 +4376,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>SE001000000000LTU73FWKBD10OF3L03V8</t>
+          <t>SE001000000000NVOTGNE4XR0Y3L26KC27</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4387,7 +4390,7 @@
         </is>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4423,22 +4426,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>43322</t>
+          <t>43366</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4453,39 +4456,39 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K38" t="n">
-        <v>93</v>
+        <v>110.5</v>
       </c>
       <c r="L38" t="n">
-        <v>102.3</v>
+        <v>121.55</v>
       </c>
       <c r="M38" t="n">
-        <v>9.300000000000001</v>
+        <v>11.05</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>SE001000000000NVOTGNE4XR0Y3L26KC27</t>
+          <t>SE001000000000ES3XR8Y7UAQ469LEVJ04</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4525,7 +4528,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4540,65 +4543,68 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>001 - IS01 - PDV 01</t>
+          <t>002 - IS01 - PDV 02</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AUGUSTO DE OLIVEIRA GOMES</t>
+          <t>BRUNO DA SILVA INACIO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>47.9</v>
+        <v>124.5</v>
       </c>
       <c r="L39" t="n">
-        <v>52.7</v>
+        <v>136.95</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>12.45</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>APT88F7A</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>SE0010000000004R1YALIDMIRV62Y25G51</t>
+          <t>632855</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PDV 02 em 54 de 67 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4612,7 +4618,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>ver observação</t>
+          <t>fechada</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -4629,7 +4635,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4644,12 +4650,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>43366</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4664,24 +4670,24 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>110.5</v>
+        <v>159</v>
       </c>
       <c r="L40" t="n">
-        <v>121.55</v>
+        <v>174.9</v>
       </c>
       <c r="M40" t="n">
-        <v>11.05</v>
+        <v>15.9</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4691,12 +4697,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>SE001000000000ES3XR8Y7UAQ469LEVJ04</t>
+          <t>263943</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4705,7 +4711,7 @@
         </is>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4736,7 +4742,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4751,12 +4757,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>43370</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4775,35 +4781,35 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
-        <v>124.5</v>
+        <v>191.5</v>
       </c>
       <c r="L41" t="n">
-        <v>136.95</v>
+        <v>210.65</v>
       </c>
       <c r="M41" t="n">
-        <v>12.45</v>
+        <v>19.15</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>632855</t>
+          <t>546604</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4812,7 +4818,7 @@
         </is>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4858,12 +4864,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>43372</t>
+          <t>43382</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4878,39 +4884,39 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="K42" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L42" t="n">
-        <v>174.9</v>
+        <v>168.3</v>
       </c>
       <c r="M42" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>263943</t>
+          <t>764107</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4919,7 +4925,7 @@
         </is>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4965,12 +4971,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:09</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4985,39 +4991,39 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>191.5</v>
+        <v>208</v>
       </c>
       <c r="L43" t="n">
-        <v>210.65</v>
+        <v>228.8</v>
       </c>
       <c r="M43" t="n">
-        <v>19.15</v>
+        <v>20.8</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>546604</t>
+          <t>493876</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5026,7 +5032,7 @@
         </is>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5057,27 +5063,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>43382</t>
+          <t>43440</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5092,39 +5098,39 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="L44" t="n">
-        <v>168.3</v>
+        <v>236.5</v>
       </c>
       <c r="M44" t="n">
-        <v>15.3</v>
+        <v>21.5</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>764107</t>
+          <t>SE001000000000F1E5AHIUVB4LQWT2EN84</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5133,7 +5139,7 @@
         </is>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5164,27 +5170,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>23:09</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5199,24 +5205,24 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="L45" t="n">
-        <v>228.8</v>
+        <v>248.6</v>
       </c>
       <c r="M45" t="n">
-        <v>20.8</v>
+        <v>22.6</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5226,12 +5232,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>493876</t>
+          <t>SE001000000000MXVG7VVGWE51FSSJG811</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5240,7 +5246,7 @@
         </is>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5286,12 +5292,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5306,39 +5312,39 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>11</v>
+        <v>240</v>
       </c>
       <c r="K46" t="n">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="L46" t="n">
-        <v>236.5</v>
+        <v>282.7</v>
       </c>
       <c r="M46" t="n">
-        <v>21.5</v>
+        <v>25.7</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>SE001000000000F1E5AHIUVB4LQWT2EN84</t>
+          <t>SE0010000000003ISIZLQVHWNRB5HNZ93D</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5347,7 +5353,7 @@
         </is>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5393,12 +5399,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5417,20 +5423,20 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="K47" t="n">
-        <v>226</v>
+        <v>52</v>
       </c>
       <c r="L47" t="n">
-        <v>248.6</v>
+        <v>57.2</v>
       </c>
       <c r="M47" t="n">
-        <v>22.6</v>
+        <v>5.2</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5440,12 +5446,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>SE001000000000MXVG7VVGWE51FSSJG811</t>
+          <t>SE00100000000043JJOUHKK5TFTY520N79</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5454,7 +5460,7 @@
         </is>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5500,12 +5506,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5520,39 +5526,39 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="K48" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L48" t="n">
-        <v>282.7</v>
+        <v>281.6</v>
       </c>
       <c r="M48" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>SE0010000000003ISIZLQVHWNRB5HNZ93D</t>
+          <t>SE001000000000GESRXQIFWGIFAKZ7ZHDS</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5561,7 +5567,7 @@
         </is>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5592,7 +5598,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5607,12 +5613,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>43454</t>
+          <t>43458</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5627,24 +5633,24 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="L49" t="n">
-        <v>57.2</v>
+        <v>249.7</v>
       </c>
       <c r="M49" t="n">
-        <v>5.2</v>
+        <v>22.7</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5654,12 +5660,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>SE00100000000043JJOUHKK5TFTY520N79</t>
+          <t>513443</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5668,7 +5674,7 @@
         </is>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5699,7 +5705,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5719,7 +5725,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>43456</t>
+          <t>43457</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5738,20 +5744,20 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>206</v>
+        <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="L50" t="n">
-        <v>281.6</v>
+        <v>310.2</v>
       </c>
       <c r="M50" t="n">
-        <v>25.6</v>
+        <v>28.2</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5761,12 +5767,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SE001000000000GESRXQIFWGIFAKZ7ZHDS</t>
+          <t>956679</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5775,7 +5781,7 @@
         </is>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5806,7 +5812,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5821,12 +5827,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5845,20 +5851,20 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="K51" t="n">
-        <v>227</v>
+        <v>103</v>
       </c>
       <c r="L51" t="n">
-        <v>249.7</v>
+        <v>113.3</v>
       </c>
       <c r="M51" t="n">
-        <v>22.7</v>
+        <v>10.3</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5868,12 +5874,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>513443</t>
+          <t>SE001000000000NZ8AH9PMU6U4GUOVUG99</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5882,7 +5888,7 @@
         </is>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5913,7 +5919,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5928,12 +5934,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>43457</t>
+          <t>43470</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5948,24 +5954,24 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>7</v>
+        <v>260</v>
       </c>
       <c r="K52" t="n">
-        <v>282</v>
+        <v>103</v>
       </c>
       <c r="L52" t="n">
-        <v>310.2</v>
+        <v>113.3</v>
       </c>
       <c r="M52" t="n">
-        <v>28.2</v>
+        <v>10.3</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5975,12 +5981,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>956679</t>
+          <t>SE001000000000LRNKOXW62WFJ77QMEKZY</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5989,7 +5995,7 @@
         </is>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6035,12 +6041,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6059,20 +6065,20 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="K53" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="L53" t="n">
-        <v>113.3</v>
+        <v>59.4</v>
       </c>
       <c r="M53" t="n">
-        <v>10.3</v>
+        <v>5.4</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -6082,12 +6088,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>SE001000000000NZ8AH9PMU6U4GUOVUG99</t>
+          <t>SE001000000000CJ48EIJX1TQFVJBXXSV4</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6142,12 +6148,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>43470</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6162,24 +6168,24 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="L54" t="n">
-        <v>113.3</v>
+        <v>187</v>
       </c>
       <c r="M54" t="n">
-        <v>10.3</v>
+        <v>17</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -6189,12 +6195,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>SE001000000000LRNKOXW62WFJ77QMEKZY</t>
+          <t>SE001000000000IG30ONROX5PIXB050M48</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6203,7 +6209,7 @@
         </is>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6234,7 +6240,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6249,12 +6255,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6273,35 +6279,35 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="L55" t="n">
-        <v>59.4</v>
+        <v>149.6</v>
       </c>
       <c r="M55" t="n">
-        <v>5.4</v>
+        <v>13.6</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>SE001000000000CJ48EIJX1TQFVJBXXSV4</t>
+          <t>160693</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -6310,7 +6316,7 @@
         </is>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6341,7 +6347,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6356,12 +6362,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>43489</t>
+          <t>43501</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6376,11 +6382,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="K56" t="n">
         <v>170</v>
@@ -6393,22 +6399,22 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>SE001000000000IG30ONROX5PIXB050M48</t>
+          <t>Z4XIlk</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6417,7 +6423,7 @@
         </is>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,7 +6454,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6463,12 +6469,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>43502</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6487,20 +6493,20 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L57" t="n">
-        <v>149.6</v>
+        <v>126.5</v>
       </c>
       <c r="M57" t="n">
-        <v>13.6</v>
+        <v>11.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6510,12 +6516,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>160693</t>
+          <t>SE001000000000NBQ8688JJKGB0KNE32D9</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6524,7 +6530,7 @@
         </is>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6555,7 +6561,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6570,12 +6576,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>43501</t>
+          <t>43507</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6590,39 +6596,39 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>28</v>
+        <v>141</v>
       </c>
       <c r="K58" t="n">
-        <v>170</v>
+        <v>307</v>
       </c>
       <c r="L58" t="n">
-        <v>187</v>
+        <v>337.7</v>
       </c>
       <c r="M58" t="n">
-        <v>17</v>
+        <v>30.7</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>22:19</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Z4XIlk</t>
+          <t>091074</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -6631,7 +6637,7 @@
         </is>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6662,27 +6668,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6701,20 +6707,20 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K59" t="n">
-        <v>115</v>
+        <v>178.5</v>
       </c>
       <c r="L59" t="n">
-        <v>126.5</v>
+        <v>196.35</v>
       </c>
       <c r="M59" t="n">
-        <v>11.5</v>
+        <v>17.85</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6724,12 +6730,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>SE001000000000NBQ8688JJKGB0KNE32D9</t>
+          <t>698660</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6774,22 +6780,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>sáb</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>43596</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6808,35 +6814,35 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>307</v>
+        <v>174</v>
       </c>
       <c r="L60" t="n">
-        <v>337.7</v>
+        <v>191.4</v>
       </c>
       <c r="M60" t="n">
-        <v>30.7</v>
+        <v>17.4</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>22:24</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>091074</t>
+          <t>663065</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6845,7 +6851,7 @@
         </is>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6876,7 +6882,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6891,12 +6897,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>43604</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6911,24 +6917,24 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K61" t="n">
-        <v>178.5</v>
+        <v>133.5</v>
       </c>
       <c r="L61" t="n">
-        <v>196.35</v>
+        <v>146.85</v>
       </c>
       <c r="M61" t="n">
-        <v>17.85</v>
+        <v>13.35</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6938,12 +6944,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>698660</t>
+          <t>SE001000000000NE499ROHU6QPYAH55Z45</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6983,7 +6989,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6998,12 +7004,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>43596</t>
+          <t>43639</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7018,39 +7024,39 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>231</v>
       </c>
       <c r="K62" t="n">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="L62" t="n">
-        <v>191.4</v>
+        <v>117.7</v>
       </c>
       <c r="M62" t="n">
-        <v>17.4</v>
+        <v>10.7</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>663065</t>
+          <t>SE001000000000NL4CQAKUYWZWXAJZYT37</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -7059,7 +7065,7 @@
         </is>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7105,12 +7111,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>43604</t>
+          <t>43643</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7125,39 +7131,39 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>12</v>
+        <v>182</v>
       </c>
       <c r="K63" t="n">
-        <v>133.5</v>
+        <v>73</v>
       </c>
       <c r="L63" t="n">
-        <v>146.85</v>
+        <v>80.3</v>
       </c>
       <c r="M63" t="n">
-        <v>13.35</v>
+        <v>7.3</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>SE001000000000NE499ROHU6QPYAH55Z45</t>
+          <t>SE001000000000LFZRJEYM9EMTS1CXAUQK</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -7166,7 +7172,7 @@
         </is>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7212,12 +7218,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7236,20 +7242,20 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>231</v>
+        <v>44</v>
       </c>
       <c r="K64" t="n">
-        <v>107</v>
+        <v>203.5</v>
       </c>
       <c r="L64" t="n">
-        <v>117.7</v>
+        <v>223.85</v>
       </c>
       <c r="M64" t="n">
-        <v>10.7</v>
+        <v>20.35</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -7259,12 +7265,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>SE001000000000NL4CQAKUYWZWXAJZYT37</t>
+          <t>SE001000000000CPB2GNUXCUNA38G6P9I7</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -7304,7 +7310,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7319,12 +7325,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>43643</t>
+          <t>43659</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7343,35 +7349,35 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="K65" t="n">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="L65" t="n">
-        <v>80.3</v>
+        <v>210.1</v>
       </c>
       <c r="M65" t="n">
-        <v>7.3</v>
+        <v>19.1</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>SE001000000000LFZRJEYM9EMTS1CXAUQK</t>
+          <t>157228</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -7380,7 +7386,7 @@
         </is>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7411,7 +7417,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7426,12 +7432,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7446,39 +7452,39 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="K66" t="n">
-        <v>203.5</v>
+        <v>173</v>
       </c>
       <c r="L66" t="n">
-        <v>223.85</v>
+        <v>190.3</v>
       </c>
       <c r="M66" t="n">
-        <v>20.35</v>
+        <v>17.3</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>SE001000000000CPB2GNUXCUNA38G6P9I7</t>
+          <t>834435</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -7487,7 +7493,7 @@
         </is>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7518,7 +7524,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7533,12 +7539,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7553,24 +7559,24 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>191</v>
+        <v>177.5</v>
       </c>
       <c r="L67" t="n">
-        <v>210.1</v>
+        <v>195.25</v>
       </c>
       <c r="M67" t="n">
-        <v>19.1</v>
+        <v>17.75</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -7580,12 +7586,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>157228</t>
+          <t>408181</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -7594,7 +7600,7 @@
         </is>
       </c>
       <c r="S67" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7640,12 +7646,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>43662</t>
+          <t>43669</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7660,24 +7666,24 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>179</v>
+        <v>46</v>
       </c>
       <c r="K68" t="n">
-        <v>173</v>
+        <v>170.5</v>
       </c>
       <c r="L68" t="n">
-        <v>190.3</v>
+        <v>187.55</v>
       </c>
       <c r="M68" t="n">
-        <v>17.3</v>
+        <v>17.05</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -7687,12 +7693,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>834435</t>
+          <t>025713</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -7701,7 +7707,7 @@
         </is>
       </c>
       <c r="S68" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7732,7 +7738,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7747,12 +7753,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>43666</t>
+          <t>43672</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -7767,24 +7773,24 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K69" t="n">
-        <v>177.5</v>
+        <v>164</v>
       </c>
       <c r="L69" t="n">
-        <v>195.25</v>
+        <v>180.4</v>
       </c>
       <c r="M69" t="n">
-        <v>17.75</v>
+        <v>16.4</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>21:59</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7794,12 +7800,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>408181</t>
+          <t>SE001000000000K5HDRBZCRIF6U919KTH0</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -7808,7 +7814,7 @@
         </is>
       </c>
       <c r="S69" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7844,22 +7850,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>43669</t>
+          <t>43863</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7874,24 +7880,24 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="K70" t="n">
-        <v>170.5</v>
+        <v>95</v>
       </c>
       <c r="L70" t="n">
-        <v>187.55</v>
+        <v>104.5</v>
       </c>
       <c r="M70" t="n">
-        <v>17.05</v>
+        <v>9.5</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7901,12 +7907,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>025713</t>
+          <t>818764</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -7915,7 +7921,7 @@
         </is>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7946,27 +7952,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>sáb</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>43865</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7981,24 +7987,24 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LUCAS DE MUSSI PALMA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K71" t="n">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="L71" t="n">
-        <v>180.4</v>
+        <v>121</v>
       </c>
       <c r="M71" t="n">
-        <v>16.4</v>
+        <v>11</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -8008,12 +8014,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>SE001000000000K5HDRBZCRIF6U919KTH0</t>
+          <t>185246</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -8022,7 +8028,7 @@
         </is>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8068,12 +8074,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>43898</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8088,24 +8094,24 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K72" t="n">
-        <v>95</v>
+        <v>271</v>
       </c>
       <c r="L72" t="n">
-        <v>104.5</v>
+        <v>298.1</v>
       </c>
       <c r="M72" t="n">
-        <v>9.5</v>
+        <v>27.1</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -8115,12 +8121,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>818764</t>
+          <t>069594</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -8129,7 +8135,7 @@
         </is>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8160,7 +8166,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8175,12 +8181,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>43919</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8195,24 +8201,24 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>110</v>
+        <v>316.5</v>
       </c>
       <c r="L73" t="n">
-        <v>121</v>
+        <v>348.15</v>
       </c>
       <c r="M73" t="n">
-        <v>11</v>
+        <v>31.65</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -8222,12 +8228,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>185246</t>
+          <t>SE001000000000KWIPD52AO3VWFGO1E4TC</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -8282,12 +8288,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>43898</t>
+          <t>43933</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8302,24 +8308,24 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K74" t="n">
-        <v>271</v>
+        <v>349.5</v>
       </c>
       <c r="L74" t="n">
-        <v>298.1</v>
+        <v>384.45</v>
       </c>
       <c r="M74" t="n">
-        <v>27.1</v>
+        <v>34.95</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -8329,12 +8335,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>069594</t>
+          <t>097612</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -8343,7 +8349,7 @@
         </is>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8379,51 +8385,54 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>qua</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>43992</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>003 - IS01 - PDV 03</t>
+          <t>002 - IS01 - PDV 02</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MARIANA CHAVES</t>
+          <t>BRUNO DA SILVA INACIO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>7</v>
       </c>
       <c r="K75" t="n">
-        <v>50.9</v>
+        <v>190</v>
       </c>
       <c r="L75" t="n">
-        <v>56</v>
+        <v>209</v>
       </c>
       <c r="M75" t="n">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -8433,21 +8442,21 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>M72267</t>
+          <t>SZEOPK</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="S75" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8461,7 +8470,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>ver observação</t>
+          <t>fechada</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -8478,27 +8487,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>43919</t>
+          <t>44045</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8513,24 +8522,24 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K76" t="n">
-        <v>316.5</v>
+        <v>166.5</v>
       </c>
       <c r="L76" t="n">
-        <v>348.15</v>
+        <v>183.15</v>
       </c>
       <c r="M76" t="n">
-        <v>31.65</v>
+        <v>16.65</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -8540,12 +8549,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>SE001000000000KWIPD52AO3VWFGO1E4TC</t>
+          <t>YGdfWb</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -8554,7 +8563,7 @@
         </is>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8590,22 +8599,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>seg</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>43933</t>
+          <t>44050</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8620,39 +8629,39 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K77" t="n">
-        <v>349.5</v>
+        <v>342</v>
       </c>
       <c r="L77" t="n">
-        <v>384.45</v>
+        <v>376.2</v>
       </c>
       <c r="M77" t="n">
-        <v>34.95</v>
+        <v>34.2</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>097612</t>
+          <t>655614</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -8661,7 +8670,7 @@
         </is>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8692,27 +8701,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>qua</t>
+          <t>qui</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>44053</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -8727,39 +8736,39 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K78" t="n">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="L78" t="n">
-        <v>209</v>
+        <v>281.6</v>
       </c>
       <c r="M78" t="n">
-        <v>19</v>
+        <v>25.6</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>SZEOPK</t>
+          <t>131765</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -8768,7 +8777,7 @@
         </is>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8799,7 +8808,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8814,12 +8823,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>44045</t>
+          <t>44062</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8838,35 +8847,35 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K79" t="n">
-        <v>166.5</v>
+        <v>103</v>
       </c>
       <c r="L79" t="n">
-        <v>183.15</v>
+        <v>113.3</v>
       </c>
       <c r="M79" t="n">
-        <v>16.65</v>
+        <v>10.3</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>APT88E4F</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>YGdfWb</t>
+          <t>SE00100000000030GP34S13B3CVBJ2XH7D</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -8875,7 +8884,7 @@
         </is>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8906,7 +8915,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8921,12 +8930,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>44050</t>
+          <t>44066</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8945,20 +8954,20 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="K80" t="n">
-        <v>342</v>
+        <v>272</v>
       </c>
       <c r="L80" t="n">
-        <v>376.2</v>
+        <v>299.2</v>
       </c>
       <c r="M80" t="n">
-        <v>34.2</v>
+        <v>27.2</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8968,12 +8977,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>655614</t>
+          <t>SE001000000000AN89T5HZ1RSPG5V5B2XE</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -8982,7 +8991,7 @@
         </is>
       </c>
       <c r="S80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9028,12 +9037,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>44053</t>
+          <t>44081</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9052,20 +9061,20 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K81" t="n">
-        <v>256</v>
+        <v>114.5</v>
       </c>
       <c r="L81" t="n">
-        <v>281.6</v>
+        <v>125.95</v>
       </c>
       <c r="M81" t="n">
-        <v>25.6</v>
+        <v>11.45</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -9075,12 +9084,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>131765</t>
+          <t>MVSSSI</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 108 de 108 casamentos exatos</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -9089,7 +9098,7 @@
         </is>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9120,27 +9129,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>44062</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9155,39 +9164,39 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K82" t="n">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L82" t="n">
-        <v>113.3</v>
+        <v>184.8</v>
       </c>
       <c r="M82" t="n">
-        <v>10.3</v>
+        <v>16.8</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>SE00100000000030GP34S13B3CVBJ2XH7D</t>
+          <t>139742</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -9196,7 +9205,7 @@
         </is>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9227,27 +9236,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>44066</t>
+          <t>44138</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9262,39 +9271,39 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>244</v>
+        <v>15</v>
       </c>
       <c r="K83" t="n">
-        <v>272</v>
+        <v>227.5</v>
       </c>
       <c r="L83" t="n">
-        <v>299.2</v>
+        <v>250.25</v>
       </c>
       <c r="M83" t="n">
-        <v>27.2</v>
+        <v>22.75</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>SE001000000000AN89T5HZ1RSPG5V5B2XE</t>
+          <t>vznBrB</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -9303,7 +9312,7 @@
         </is>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9334,27 +9343,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>44157</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -9369,39 +9378,39 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>114.5</v>
+        <v>138</v>
       </c>
       <c r="L84" t="n">
-        <v>125.95</v>
+        <v>151.8</v>
       </c>
       <c r="M84" t="n">
-        <v>11.45</v>
+        <v>13.8</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>APT88E4F</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>MVSSSI</t>
+          <t>080164</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PDV 02 em 87 de 88 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -9410,7 +9419,7 @@
         </is>
       </c>
       <c r="S84" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9456,12 +9465,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>44163</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9476,24 +9485,24 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K85" t="n">
-        <v>168</v>
+        <v>158.5</v>
       </c>
       <c r="L85" t="n">
-        <v>184.8</v>
+        <v>174.35</v>
       </c>
       <c r="M85" t="n">
-        <v>16.8</v>
+        <v>15.85</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -9503,12 +9512,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>139742</t>
+          <t>685816</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -9548,7 +9557,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9563,12 +9572,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>44138</t>
+          <t>44170</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9587,20 +9596,20 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K86" t="n">
-        <v>227.5</v>
+        <v>212.5</v>
       </c>
       <c r="L86" t="n">
-        <v>250.25</v>
+        <v>233.75</v>
       </c>
       <c r="M86" t="n">
-        <v>22.75</v>
+        <v>21.25</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -9610,12 +9619,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>vznBrB</t>
+          <t>415759</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -9624,7 +9633,7 @@
         </is>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9655,7 +9664,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9670,12 +9679,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9690,24 +9699,24 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+          <t>DAVID FERNANDES DA CRUZ</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>227</v>
       </c>
       <c r="K87" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="L87" t="n">
-        <v>151.8</v>
+        <v>128.7</v>
       </c>
       <c r="M87" t="n">
-        <v>13.8</v>
+        <v>11.7</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -9717,12 +9726,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>080164</t>
+          <t>SE001000000000J14Q1TG3DZUVC81ORKC1</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -9731,7 +9740,7 @@
         </is>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9767,22 +9776,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9801,44 +9810,44 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K88" t="n">
-        <v>158.5</v>
+        <v>347.5</v>
       </c>
       <c r="L88" t="n">
-        <v>174.35</v>
+        <v>382.25</v>
       </c>
       <c r="M88" t="n">
-        <v>15.85</v>
+        <v>34.75</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>APT88F78</t>
+          <t>CLF2C662</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>685816</t>
+          <t>050671</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 03 em 3 de 3 casamentos exatos</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>não</t>
         </is>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9852,7 +9861,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>fechada</t>
+          <t>ver observação</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -9869,27 +9878,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>44170</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9904,24 +9913,24 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K89" t="n">
-        <v>212.5</v>
+        <v>220</v>
       </c>
       <c r="L89" t="n">
-        <v>233.75</v>
+        <v>242</v>
       </c>
       <c r="M89" t="n">
-        <v>21.25</v>
+        <v>22</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -9931,12 +9940,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>415759</t>
+          <t>SE001000000000J26ZYARRMKJWH476N892</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -9945,7 +9954,7 @@
         </is>
       </c>
       <c r="S89" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9981,22 +9990,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44559</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -10011,24 +10020,24 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DAVID FERNANDES DA CRUZ</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>227</v>
+        <v>3</v>
       </c>
       <c r="K90" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="L90" t="n">
-        <v>128.7</v>
+        <v>176</v>
       </c>
       <c r="M90" t="n">
-        <v>11.7</v>
+        <v>16</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -10038,12 +10047,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>SE001000000000J14Q1TG3DZUVC81ORKC1</t>
+          <t>SE001000000000KWTAY4C457ZT2V9UCL55</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -10052,7 +10061,7 @@
         </is>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10098,12 +10107,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>44561</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -10118,48 +10127,48 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="K91" t="n">
-        <v>347.5</v>
+        <v>144</v>
       </c>
       <c r="L91" t="n">
-        <v>382.25</v>
+        <v>158.4</v>
       </c>
       <c r="M91" t="n">
-        <v>34.75</v>
+        <v>14.4</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>CLF2C662</t>
+          <t>APT88F78</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>050671</t>
+          <t>681885</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PDV 03 em 4 de 4 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10173,7 +10182,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>ver observação</t>
+          <t>fechada</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -10190,7 +10199,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10205,12 +10214,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -10225,24 +10234,24 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K92" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="L92" t="n">
-        <v>242</v>
+        <v>280.5</v>
       </c>
       <c r="M92" t="n">
-        <v>22</v>
+        <v>25.5</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -10252,12 +10261,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>SE001000000000J26ZYARRMKJWH476N892</t>
+          <t>263017</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -10266,7 +10275,7 @@
         </is>
       </c>
       <c r="S92" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10297,7 +10306,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10312,12 +10321,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>44573</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -10336,44 +10345,44 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>214</v>
+      </c>
+      <c r="K93" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="L93" t="n">
+        <v>160.05</v>
+      </c>
+      <c r="M93" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>APT88F78</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>348947</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="S93" t="n">
         <v>3</v>
-      </c>
-      <c r="K93" t="n">
-        <v>160</v>
-      </c>
-      <c r="L93" t="n">
-        <v>176</v>
-      </c>
-      <c r="M93" t="n">
-        <v>16</v>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>21:22</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>APT88F78</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>SE001000000000KWTAY4C457ZT2V9UCL55</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="S93" t="n">
-        <v>1</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10404,7 +10413,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10419,12 +10428,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>44561</t>
+          <t>44584</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -10439,24 +10448,24 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>KEROLAINY LAWANY RIO BRANCO</t>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K94" t="n">
-        <v>144</v>
+        <v>257</v>
       </c>
       <c r="L94" t="n">
-        <v>158.4</v>
+        <v>282.7</v>
       </c>
       <c r="M94" t="n">
-        <v>14.4</v>
+        <v>25.7</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -10466,12 +10475,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>681885</t>
+          <t>FDU3XH</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
+          <t>PDV 02 em 132 de 132 casamentos exatos</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -10480,7 +10489,7 @@
         </is>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10498,327 +10507,6 @@
         </is>
       </c>
       <c r="W94" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>ISAIAS 01 - MARINGA</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Débito</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>seg</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>22:01</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>44571</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>002 - IS01 - PDV 02</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>BRUNO DA SILVA INACIO</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>26</v>
-      </c>
-      <c r="K95" t="n">
-        <v>255</v>
-      </c>
-      <c r="L95" t="n">
-        <v>280.5</v>
-      </c>
-      <c r="M95" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>21:42</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>APT88F78</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>263017</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="S95" t="n">
-        <v>19</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>nenhum</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>fechada</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ISAIAS 01 - MARINGA</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Débito</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>seg</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>22:05</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>44573</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>002 - IS01 - PDV 02</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>BRUNO DA SILVA INACIO</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>214</v>
-      </c>
-      <c r="K96" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="L96" t="n">
-        <v>160.05</v>
-      </c>
-      <c r="M96" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>22:02</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>APT88F78</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>348947</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="S96" t="n">
-        <v>3</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>nenhum</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>fechada</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>ISAIAS 01 - MARINGA</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Débito</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>seg</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>22:51</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>44584</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>002 - IS01 - PDV 02</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>BRUNO DA SILVA INACIO</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>8</v>
-      </c>
-      <c r="K97" t="n">
-        <v>257</v>
-      </c>
-      <c r="L97" t="n">
-        <v>282.7</v>
-      </c>
-      <c r="M97" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>22:44</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>APT88F78</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>FDU3XH</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>PDV 02 em 97 de 97 casamentos exatos</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="S97" t="n">
-        <v>7</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>nenhum</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>fechada</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
         <is>
           <t>não</t>
         </is>
@@ -10835,10 +10523,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -10867,10 +10555,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>1590.7</v>
+        <v>1585.6</v>
       </c>
     </row>
     <row r="3">
@@ -10884,32 +10572,6 @@
       </c>
       <c r="C3" t="n">
         <v>22.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AUGUSTO DE OLIVEIRA GOMES</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.8</v>
       </c>
     </row>
   </sheetData>
@@ -10929,7 +10591,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11038,10 +10700,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>42.5</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="7">
@@ -11074,10 +10736,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>99.45</v>
+        <v>94.65000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -11128,10 +10790,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>119.3</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="12">
